--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129001023</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129001023</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129001023</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129001023</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129001023</v>
       </c>
       <c r="B5" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129001023</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>129001023</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129001036</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676958</v>
+        <v>129001023</v>
       </c>
       <c r="B2" t="n">
-        <v>97881</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578232</v>
+        <v>578212</v>
       </c>
       <c r="R2" t="n">
-        <v>6731920</v>
+        <v>6731849</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,42 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676960</v>
+        <v>129001031</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578182</v>
+        <v>578122</v>
       </c>
       <c r="R3" t="n">
-        <v>6731920</v>
+        <v>6731888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -900,12 +890,7 @@
         <v>118676959</v>
       </c>
       <c r="B4" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129001023</v>
+        <v>118676958</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578212</v>
+        <v>578232</v>
       </c>
       <c r="R5" t="n">
-        <v>6731849</v>
+        <v>6731920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1114,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129001036</v>
+        <v>118676960</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,7 +1129,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578158</v>
+        <v>578182</v>
       </c>
       <c r="R6" t="n">
-        <v>6731986</v>
+        <v>6731920</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1223,7 +1208,7 @@
         <v>129001035</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,6 +1308,854 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129001036</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>578158</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6731986</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129001037</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578175</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6732015</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129001038</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>578162</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6732023</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129001040</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578161</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6732018</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129001041</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>578163</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6732018</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129001042</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>578160</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6732007</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129001043</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>578159</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6732007</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129001044</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kungsberg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>578154</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6732019</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52782-2025 artfynd.xlsx
+++ b/artfynd/A 52782-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676959</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676958</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676960</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001035</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001036</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001037</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001038</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001040</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001041</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001042</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001043</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,8 +2226,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001044</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>